--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-practitionerrole.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-practitionerrole.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Human Overseer (PractitionerRole)</t>
+    <t>EU AI Practitioner Role</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Defines the qualifications, specialty, and AI-specific training of the human responsible for oversight of the AI system, as required by the AI Act (HL-02).</t>
+    <t>A PractitionerRole profile representing the role, qualification context, specialty, and AI-related training information of the human reviewer involved in oversight of an AI-supported workflow.</t>
   </si>
   <si>
     <t>Purpose</t>
